--- a/Steam Achievements Stable.xlsx
+++ b/Steam Achievements Stable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CJ\Documents\My Projects\My Skill Development\game-achievement-data\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7D2A7F-8521-4275-879A-1855C584D13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D8BBB1-CB37-454A-9805-8D81D3E1947E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="10" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2592" uniqueCount="1286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3131" uniqueCount="1555">
   <si>
     <t>Game</t>
   </si>
@@ -3897,6 +3897,813 @@
   </si>
   <si>
     <t>Year</t>
+  </si>
+  <si>
+    <t>Onimusha: Way of the Sword</t>
+  </si>
+  <si>
+    <t>Onimusha Showdown</t>
+  </si>
+  <si>
+    <t>Drive off Sasaki Ganryu.</t>
+  </si>
+  <si>
+    <t>https://shared.fastly.steamstatic.com/community_assets/images/apps/2638890/0a1386e0b924db19aa90b5667dcec01a36511d48.jpg</t>
+  </si>
+  <si>
+    <t>Get This Thing Off Me</t>
+  </si>
+  <si>
+    <t>Absorb 30 or more souls at once.</t>
+  </si>
+  <si>
+    <t>https://shared.fastly.steamstatic.com/community_assets/images/apps/2638890/6df5400daef82f23e33ff79dd4774dfa430fb0fd.jpg</t>
+  </si>
+  <si>
+    <t>Get Stuffed</t>
+  </si>
+  <si>
+    <t>Defeat Daidara.</t>
+  </si>
+  <si>
+    <t>Looking Sharp</t>
+  </si>
+  <si>
+    <t>Enhance a piece of equipment for the first time.</t>
+  </si>
+  <si>
+    <t>Twisted Fates</t>
+  </si>
+  <si>
+    <t>Defeat Rasho-gan.</t>
+  </si>
+  <si>
+    <t>Berserker</t>
+  </si>
+  <si>
+    <t>Defeat 3 enemies with continuous Break Issen attacks.</t>
+  </si>
+  <si>
+    <t>Howling Wind</t>
+  </si>
+  <si>
+    <t>Defeat Ifuu.</t>
+  </si>
+  <si>
+    <t>Life-Saver</t>
+  </si>
+  <si>
+    <t>Complete your first Chance Encounter.</t>
+  </si>
+  <si>
+    <t>Dokyo's Fixation</t>
+  </si>
+  <si>
+    <t>Defeat the Greater Nue.</t>
+  </si>
+  <si>
+    <t>Second Helping</t>
+  </si>
+  <si>
+    <t>Beat an opponent in a Boss Rematch.</t>
+  </si>
+  <si>
+    <t>No Dog Left Behind</t>
+  </si>
+  <si>
+    <t>Rescue your first Lion Dog.</t>
+  </si>
+  <si>
+    <t>Mystery Solved</t>
+  </si>
+  <si>
+    <t>Complete your first Mystery of Kyoto.</t>
+  </si>
+  <si>
+    <t>Winning Is What Matters</t>
+  </si>
+  <si>
+    <t>Carry out 50 attacks with environmental objects.</t>
+  </si>
+  <si>
+    <t>A Real Charmer</t>
+  </si>
+  <si>
+    <t>Enhance a charm to the maximum level.</t>
+  </si>
+  <si>
+    <t>Benkei: Out, but Not Down</t>
+  </si>
+  <si>
+    <t>Defeat Benkei.</t>
+  </si>
+  <si>
+    <t>Serves You Right</t>
+  </si>
+  <si>
+    <t>Defeat the Byakue at Kiyomizu-dera Temple.</t>
+  </si>
+  <si>
+    <t>Helm Splitter</t>
+  </si>
+  <si>
+    <t>Break 100 shields or pieces of enemy armor.</t>
+  </si>
+  <si>
+    <t>Crashing Lightning</t>
+  </si>
+  <si>
+    <t>Defeat Burai.</t>
+  </si>
+  <si>
+    <t>Burning Blade</t>
+  </si>
+  <si>
+    <t>Defeat 50 foes while in the Blazing State.</t>
+  </si>
+  <si>
+    <t>Untouchable</t>
+  </si>
+  <si>
+    <t>Perform 50 Grab Reversals.</t>
+  </si>
+  <si>
+    <t>Coming Through!</t>
+  </si>
+  <si>
+    <t>Break an enemy's guard 50 times.</t>
+  </si>
+  <si>
+    <t>Selfish Selflessness</t>
+  </si>
+  <si>
+    <t>Rescue a merchant that's being attacked by Genma.</t>
+  </si>
+  <si>
+    <t>Brutalist</t>
+  </si>
+  <si>
+    <t>Land 50 Issen attacks.</t>
+  </si>
+  <si>
+    <t>Wide Awake</t>
+  </si>
+  <si>
+    <t>Defeat Shuten Doji.</t>
+  </si>
+  <si>
+    <t>Health Is Wealth</t>
+  </si>
+  <si>
+    <t>Enhance a Hozuki Pouch to the maximum level.</t>
+  </si>
+  <si>
+    <t>The Perfect Storm</t>
+  </si>
+  <si>
+    <t>Defeat Ifuu and Burai.</t>
+  </si>
+  <si>
+    <t>Deadeye</t>
+  </si>
+  <si>
+    <t>Score 100 headshots with your bow.</t>
+  </si>
+  <si>
+    <t>Stop Motion</t>
+  </si>
+  <si>
+    <t>Perform 50 Reflex Combos.</t>
+  </si>
+  <si>
+    <t>We Done Here?</t>
+  </si>
+  <si>
+    <t>Defeat Sasaki Ganryu at Arashiyama.</t>
+  </si>
+  <si>
+    <t>Pinch Hitter</t>
+  </si>
+  <si>
+    <t>Deflect 50 projectiles.</t>
+  </si>
+  <si>
+    <t>Silent Violence</t>
+  </si>
+  <si>
+    <t>Assassinate 20 enemies.</t>
+  </si>
+  <si>
+    <t>End This Madness</t>
+  </si>
+  <si>
+    <t>Defeat Dokyo.</t>
+  </si>
+  <si>
+    <t>Demystified</t>
+  </si>
+  <si>
+    <t>Complete all Mysteries of Kyoto.</t>
+  </si>
+  <si>
+    <t>Baited by Benkei</t>
+  </si>
+  <si>
+    <t>Defeat Benkei at Rendaino.</t>
+  </si>
+  <si>
+    <t>Oni Armory</t>
+  </si>
+  <si>
+    <t>Acquire all Oni Armaments.</t>
+  </si>
+  <si>
+    <t>Truly, Thank You</t>
+  </si>
+  <si>
+    <t>Defeat Minamoto no Yoshitsune.</t>
+  </si>
+  <si>
+    <t>No Job Too Small</t>
+  </si>
+  <si>
+    <t>Complete all Chance Encounters.</t>
+  </si>
+  <si>
+    <t>For the Love of Dog</t>
+  </si>
+  <si>
+    <t>Rescue all the Lion Dogs.</t>
+  </si>
+  <si>
+    <t>Wielder of Oni Armaments</t>
+  </si>
+  <si>
+    <t>Defeat 100 enemies with Oni Armaments.</t>
+  </si>
+  <si>
+    <t>The Winding Way of the Sword</t>
+  </si>
+  <si>
+    <t>Learn and upgrade all basic or special skills.</t>
+  </si>
+  <si>
+    <t>Enhance all equipment to the maximum level.</t>
+  </si>
+  <si>
+    <t>Well-Rounded</t>
+  </si>
+  <si>
+    <t>Learn and upgrade all basic and special skills.</t>
+  </si>
+  <si>
+    <t>Flow State</t>
+  </si>
+  <si>
+    <t>Defeat 50 enemies with Chain Issen attacks.</t>
+  </si>
+  <si>
+    <t>Citizen Savior</t>
+  </si>
+  <si>
+    <t>Rescue 30 townspeople from marauding Genma.</t>
+  </si>
+  <si>
+    <t>Oni's Oni</t>
+  </si>
+  <si>
+    <t>Defeat 50 enemies in the Oni Awakened state.</t>
+  </si>
+  <si>
+    <t>Medical Marvel</t>
+  </si>
+  <si>
+    <t>Enhance all Hozuki Pouches to the maximum level.</t>
+  </si>
+  <si>
+    <t>Genma Griller</t>
+  </si>
+  <si>
+    <t>Set three enemies ablaze at once.</t>
+  </si>
+  <si>
+    <t>Charmed Life</t>
+  </si>
+  <si>
+    <t>Enhance all charms to the maximum level.</t>
+  </si>
+  <si>
+    <t>Genma-ologist</t>
+  </si>
+  <si>
+    <t>Collect all the Genma notes.</t>
+  </si>
+  <si>
+    <t>True Onimusha</t>
+  </si>
+  <si>
+    <t>Complete the game on difficulty level "Carnage".</t>
+  </si>
+  <si>
+    <t>Glutton for Punishment</t>
+  </si>
+  <si>
+    <t>Beat all Boss Rematch opponents on all difficulty levels.</t>
+  </si>
+  <si>
+    <t>Peerless</t>
+  </si>
+  <si>
+    <t>Unlock all achievements.</t>
+  </si>
+  <si>
+    <t>sales_vg_insights</t>
+  </si>
+  <si>
+    <t>Nine Sols</t>
+  </si>
+  <si>
+    <t>My Revenge Starts Here</t>
+  </si>
+  <si>
+    <t>Defeat Baichang.</t>
+  </si>
+  <si>
+    <t>https://shared.fastly.steamstatic.com/community_assets/images/apps/1809540/ca9a9a14d38e544a2edb077827f195baae480558.jpg</t>
+  </si>
+  <si>
+    <t>I'm Coming for You, Old Friend</t>
+  </si>
+  <si>
+    <t>Defeat Yingzhao.</t>
+  </si>
+  <si>
+    <t>https://shared.fastly.steamstatic.com/community_assets/images/apps/1809540/034d35829e92d3ebd7743eff871e3111999aa2f9.jpg</t>
+  </si>
+  <si>
+    <t>Reap What You Sow</t>
+  </si>
+  <si>
+    <t>Defeat Goumang.</t>
+  </si>
+  <si>
+    <t>You Should Respect Your Elders</t>
+  </si>
+  <si>
+    <t>Defeat Yanlao.</t>
+  </si>
+  <si>
+    <t>Jail Break</t>
+  </si>
+  <si>
+    <t>Successfully escape from prison.</t>
+  </si>
+  <si>
+    <t>No Pain, No Gain</t>
+  </si>
+  <si>
+    <t>Defeat Jiequan.</t>
+  </si>
+  <si>
+    <t>Wake Up From My Sin</t>
+  </si>
+  <si>
+    <t>Defeat Lady Ethereal.</t>
+  </si>
+  <si>
+    <t>The Cavalry's Here</t>
+  </si>
+  <si>
+    <t>Rescue the people of the Peach Blossom Village.</t>
+  </si>
+  <si>
+    <t>Do Re Mi So La</t>
+  </si>
+  <si>
+    <t>Unravel the mystery of the Daybreak Tower's music sheet.</t>
+  </si>
+  <si>
+    <t>Come, Sweet Death</t>
+  </si>
+  <si>
+    <t>Defeat Ji.</t>
+  </si>
+  <si>
+    <t>We Have Each Other</t>
+  </si>
+  <si>
+    <t>Defeat Fuxi and Nuwa.</t>
+  </si>
+  <si>
+    <t>Gimme Gimme</t>
+  </si>
+  <si>
+    <t>Establish a deep relationship with Shuanshuan.</t>
+  </si>
+  <si>
+    <t>Across Time and Space</t>
+  </si>
+  <si>
+    <t>Bid farewell to Lear.</t>
+  </si>
+  <si>
+    <t>Magical Bean</t>
+  </si>
+  <si>
+    <t>Help Shuanshuan unlock the true potential of agriculture.</t>
+  </si>
+  <si>
+    <t>Fight Dirty</t>
+  </si>
+  <si>
+    <t>Use the Gene Eradicator to fight Jiequan.</t>
+  </si>
+  <si>
+    <t>You Bastard...</t>
+  </si>
+  <si>
+    <t>Obtain map data from Shanhai 9000 by force.</t>
+  </si>
+  <si>
+    <t>Stonks!</t>
+  </si>
+  <si>
+    <t>Recycle Shuanshuan's coin.</t>
+  </si>
+  <si>
+    <t>Evolution</t>
+  </si>
+  <si>
+    <t>Discover a tremendous secret.</t>
+  </si>
+  <si>
+    <t>Learned From the Best</t>
+  </si>
+  <si>
+    <t>Defeat Eigong.</t>
+  </si>
+  <si>
+    <t>One Man Army</t>
+  </si>
+  <si>
+    <t>Defeat every optional miniboss.</t>
+  </si>
+  <si>
+    <t>I'm Yi, I Have a Drinking Problem</t>
+  </si>
+  <si>
+    <t>Drink all the wine brewed by Shennong.</t>
+  </si>
+  <si>
+    <t>Blessed Messages</t>
+  </si>
+  <si>
+    <t>Discover the message board for blessings upon the Departure of New Kunlun's Voyage.</t>
+  </si>
+  <si>
+    <t>Passing on the Torch</t>
+  </si>
+  <si>
+    <t>Help Shennong become the leader of Peach Blossom Village.</t>
+  </si>
+  <si>
+    <t>Fight Through Hardship</t>
+  </si>
+  <si>
+    <t>Finish Nine Sols on Standard Mode.</t>
+  </si>
+  <si>
+    <t>The Warrior Within</t>
+  </si>
+  <si>
+    <t>Master all skills in the skill tree.</t>
+  </si>
+  <si>
+    <t>Well Prepared</t>
+  </si>
+  <si>
+    <t>Collect every Jade.</t>
+  </si>
+  <si>
+    <t>Home Sweet Home</t>
+  </si>
+  <si>
+    <t>Return to the home world of Solarian.</t>
+  </si>
+  <si>
+    <t>Found You</t>
+  </si>
+  <si>
+    <t>Help Shanhai 9000 find Chien.</t>
+  </si>
+  <si>
+    <t>Shooting Star</t>
+  </si>
+  <si>
+    <t>Witness the end of New Kunlun.</t>
+  </si>
+  <si>
+    <t>My Most Trusted Friend</t>
+  </si>
+  <si>
+    <t>Max out the ammo capacity of the Azure Bow and obtain Cloud Piercer X, Thunder Buster X, and Shadow Hunter X.</t>
+  </si>
+  <si>
+    <t>Rest for the Wicked</t>
+  </si>
+  <si>
+    <t>Help Chiyou bring peace to Xingtian.</t>
+  </si>
+  <si>
+    <t>What Have You Done?!</t>
+  </si>
+  <si>
+    <t>Break the clay pot made by Shuanshuan</t>
+  </si>
+  <si>
+    <t>Repurposed</t>
+  </si>
+  <si>
+    <t>Use the Fortune teller machine crafted by Shuanshuan.</t>
+  </si>
+  <si>
+    <t>Treasure Hunter</t>
+  </si>
+  <si>
+    <t>Find all resources and information marked by Shanhai 9000.</t>
+  </si>
+  <si>
+    <t>Robo Fight!</t>
+  </si>
+  <si>
+    <t>Defeat Tianshou while driving a robot.</t>
+  </si>
+  <si>
+    <t>Dark Souls III</t>
+  </si>
+  <si>
+    <t>Enkindle</t>
+  </si>
+  <si>
+    <t>Light a bonfire flame for the first time.</t>
+  </si>
+  <si>
+    <t>https://shared.fastly.steamstatic.com/community_assets/images/apps/374320/1595b7bf2058e67673875eedb18e3d1838460d67.jpg</t>
+  </si>
+  <si>
+    <t>Embrace the Flame</t>
+  </si>
+  <si>
+    <t>Become a Host of Embers for the first time.</t>
+  </si>
+  <si>
+    <t>https://shared.fastly.steamstatic.com/community_assets/images/apps/374320/512e7a3273961258de448adf58b89370f2cb26f6.jpg</t>
+  </si>
+  <si>
+    <t>Iudex Gundyr</t>
+  </si>
+  <si>
+    <t>Defeat Iudex Gundyr.</t>
+  </si>
+  <si>
+    <t>Vordt of the Boreal Valley</t>
+  </si>
+  <si>
+    <t>Defeat Vordt of the Boreal Valley.</t>
+  </si>
+  <si>
+    <t>Covenant: Way of Blue</t>
+  </si>
+  <si>
+    <t>Discover Way of Blue covenant.</t>
+  </si>
+  <si>
+    <t>Curse-rotted Greatwood</t>
+  </si>
+  <si>
+    <t>Defeat the Curse-rotted Greatwood.</t>
+  </si>
+  <si>
+    <t>Covenant: Blue Sentinels</t>
+  </si>
+  <si>
+    <t>Discover Blue Sentinels covenant.</t>
+  </si>
+  <si>
+    <t>Crystal Sage</t>
+  </si>
+  <si>
+    <t>Defeat Crystal Sage.</t>
+  </si>
+  <si>
+    <t>Lords of Cinder: Abyss Watchers</t>
+  </si>
+  <si>
+    <t>Defeat the Abyss Watchers, Lords of Cinder.</t>
+  </si>
+  <si>
+    <t>Deacons of the Deep</t>
+  </si>
+  <si>
+    <t>Defeat the Deacons of the Deep.</t>
+  </si>
+  <si>
+    <t>High Lord Wolnir</t>
+  </si>
+  <si>
+    <t>Defeat High Lord Wolnir.</t>
+  </si>
+  <si>
+    <t>Covenant: Warrior of Sunlight</t>
+  </si>
+  <si>
+    <t>Discover Warrior of Sunlight covenant.</t>
+  </si>
+  <si>
+    <t>Pontiff Sulyvahn</t>
+  </si>
+  <si>
+    <t>Defeat Pontiff Sulyvahn.</t>
+  </si>
+  <si>
+    <t>Covenant: Watchdogs of Farron</t>
+  </si>
+  <si>
+    <t>Discover Watchdogs of Farron covenant.</t>
+  </si>
+  <si>
+    <t>Dancer of the Boreal Valley</t>
+  </si>
+  <si>
+    <t>Defeat Dancer of the Boreal Valley.</t>
+  </si>
+  <si>
+    <t>Lord of Cinder: Aldrich, Devourer of Gods</t>
+  </si>
+  <si>
+    <t>Defeat Aldrich, Devourer of Gods, Lord of Cinder.</t>
+  </si>
+  <si>
+    <t>Lord of Cinder: Yhorm the Giant</t>
+  </si>
+  <si>
+    <t>Defeat Yhorm the Giant, Lord of Cinder.</t>
+  </si>
+  <si>
+    <t>Old Demon King</t>
+  </si>
+  <si>
+    <t>Defeat Old Demon King.</t>
+  </si>
+  <si>
+    <t>Dragonslayer Armour</t>
+  </si>
+  <si>
+    <t>Defeat Dragonslayer Armour.</t>
+  </si>
+  <si>
+    <t>Oceiros, the Consumed King</t>
+  </si>
+  <si>
+    <t>Defeat Oceiros, the Consumed King.</t>
+  </si>
+  <si>
+    <t>Untended Graves</t>
+  </si>
+  <si>
+    <t>Reach the Untended Graves.</t>
+  </si>
+  <si>
+    <t>Covenant: Rosaria's Fingers</t>
+  </si>
+  <si>
+    <t>Discover Rosaria's Fingers covenant.</t>
+  </si>
+  <si>
+    <t>Lord of Cinder: Lothric, Younger Prince</t>
+  </si>
+  <si>
+    <t>Defeat Lothric, Younger Prince, Lord of Cinder.</t>
+  </si>
+  <si>
+    <t>Champion Gundyr</t>
+  </si>
+  <si>
+    <t>Defeat Champion Gundyr.</t>
+  </si>
+  <si>
+    <t>Supreme Weapon Reinforcement</t>
+  </si>
+  <si>
+    <t>Reinforce any weapon to the highest level.</t>
+  </si>
+  <si>
+    <t>Archdragon Peak</t>
+  </si>
+  <si>
+    <t>Reach Archdragon Peak.</t>
+  </si>
+  <si>
+    <t>Ancient Wyvern</t>
+  </si>
+  <si>
+    <t>Defeat Ancient Wyvern.</t>
+  </si>
+  <si>
+    <t>The Nameless King</t>
+  </si>
+  <si>
+    <t>Defeat Nameless King.</t>
+  </si>
+  <si>
+    <t>Covenant: Mound-makers</t>
+  </si>
+  <si>
+    <t>Discover Mound-makers covenant.</t>
+  </si>
+  <si>
+    <t>Covenant: Aldrich Faithful</t>
+  </si>
+  <si>
+    <t>Discover Aldrich Faithful covenant.</t>
+  </si>
+  <si>
+    <t>Ultimate Bonfire</t>
+  </si>
+  <si>
+    <t>Reinforce a bonfire to the highest level.</t>
+  </si>
+  <si>
+    <t>Covenant: Blade of the Darkmoon</t>
+  </si>
+  <si>
+    <t>Discover Blade of the Darkmoon covenant.</t>
+  </si>
+  <si>
+    <t>Ultimate Estus</t>
+  </si>
+  <si>
+    <t>Reinforce the Estus Flask to the highest level.</t>
+  </si>
+  <si>
+    <t>To Link the First Flame</t>
+  </si>
+  <si>
+    <t>Reach "To Link the First Flame" ending.</t>
+  </si>
+  <si>
+    <t>The End of Fire</t>
+  </si>
+  <si>
+    <t>Reach "The End of Fire" ending.</t>
+  </si>
+  <si>
+    <t>The Usurpation of Fire</t>
+  </si>
+  <si>
+    <t>Reach "The Usurpation of Fire" ending.</t>
+  </si>
+  <si>
+    <t>Master of Infusion</t>
+  </si>
+  <si>
+    <t>Perform all forms of infusion.</t>
+  </si>
+  <si>
+    <t>Master of Sorceries</t>
+  </si>
+  <si>
+    <t>Acquire all sorceries.</t>
+  </si>
+  <si>
+    <t>Master of Pyromancies</t>
+  </si>
+  <si>
+    <t>Acquire all pyromancies.</t>
+  </si>
+  <si>
+    <t>Master of Miracles</t>
+  </si>
+  <si>
+    <t>Acquire all miracles.</t>
+  </si>
+  <si>
+    <t>Master of Expression</t>
+  </si>
+  <si>
+    <t>Master of Rings</t>
+  </si>
+  <si>
+    <t>Acquire all rings.</t>
+  </si>
+  <si>
+    <t>The Dark Soul</t>
+  </si>
+  <si>
+    <t>Complete all achievements.</t>
+  </si>
+  <si>
+    <t>Last point before multiple endings</t>
   </si>
 </sst>
 </file>
@@ -3942,7 +4749,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -3976,6 +4783,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3985,7 +4805,7 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -4004,6 +4824,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -12163,7 +12989,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9ED5556E-4C6A-47E3-B282-BE5BF48AC4E6}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9ED5556E-4C6A-47E3-B282-BE5BF48AC4E6}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A1:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -12277,8 +13103,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F859DB1-FF23-4CA9-91E6-692EDA0BDA7D}" name="Table1" displayName="Table1" ref="A1:J620" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:J620" xr:uid="{4F859DB1-FF23-4CA9-91E6-692EDA0BDA7D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F859DB1-FF23-4CA9-91E6-692EDA0BDA7D}" name="Table1" displayName="Table1" ref="A1:J750" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:J750" xr:uid="{4F859DB1-FF23-4CA9-91E6-692EDA0BDA7D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J620">
     <sortCondition ref="B1:B620"/>
   </sortState>
@@ -12293,7 +13119,7 @@
     <tableColumn id="10" xr3:uid="{9CA9A0F1-F0C2-476A-9B2E-6E9F8CDEECD7}" name="Marker_ID" dataDxfId="2">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{EAC75395-7F2E-4269-846C-F0D0F7802287}" name="Year" dataDxfId="0">
+    <tableColumn id="8" xr3:uid="{EAC75395-7F2E-4269-846C-F0D0F7802287}" name="Year" dataDxfId="1">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{CFD742E9-2398-4FA3-A21B-705B056B1C95}" name="Notes"/>
@@ -12303,18 +13129,19 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9ACA679-95B1-4F13-8E1B-ECA817DD0293}" name="Table14" displayName="Table14" ref="A1:E13" totalsRowShown="0">
-  <autoFilter ref="A1:E13" xr:uid="{F9ACA679-95B1-4F13-8E1B-ECA817DD0293}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9ACA679-95B1-4F13-8E1B-ECA817DD0293}" name="Table14" displayName="Table14" ref="A1:F16" totalsRowShown="0">
+  <autoFilter ref="A1:F16" xr:uid="{F9ACA679-95B1-4F13-8E1B-ECA817DD0293}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{FBD9D949-73B1-4C90-B6F6-B46C8BAD53DA}" name="ID">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{28EB75C3-33D2-4E57-B68F-AE210B54904F}" name="Game"/>
     <tableColumn id="3" xr3:uid="{CFE407BB-33AA-4705-AD25-B9B672CF2C6D}" name="game_id"/>
-    <tableColumn id="4" xr3:uid="{E6D5A2DE-AF03-4A0B-9C44-037642A46489}" name="game_link" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{E6D5A2DE-AF03-4A0B-9C44-037642A46489}" name="game_link" dataDxfId="0">
       <calculatedColumnFormula>"https://steamdb.info/app/"&amp;Table14[[#This Row],[game_id]]&amp;"/stats/"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{CCFC4D96-02C0-4F0C-8FAD-D0D12E1423D9}" name="release_year"/>
+    <tableColumn id="6" xr3:uid="{8D44AAE4-90C4-4ECF-950E-C88E5C3C4973}" name="sales_vg_insights"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12730,7 +13557,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J620"/>
+  <dimension ref="A1:J750"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" customWidth="1"/>
@@ -30296,6 +31123,3693 @@
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
         <v>2022</v>
       </c>
+    </row>
+    <row r="621" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A621" s="1">
+        <v>0</v>
+      </c>
+      <c r="B621" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C621" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D621" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E621" s="4">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="F621" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G621" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H621">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>2</v>
+      </c>
+      <c r="I621">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="622" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A622" s="1">
+        <v>1</v>
+      </c>
+      <c r="B622" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C622" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D622" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E622" s="4">
+        <v>0.87400000000000011</v>
+      </c>
+      <c r="F622" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H622">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I622">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="623" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A623" s="1">
+        <v>2</v>
+      </c>
+      <c r="B623" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C623" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D623" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E623" s="4">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="F623" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H623">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I623">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="624" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A624" s="1">
+        <v>3</v>
+      </c>
+      <c r="B624" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C624" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D624" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E624" s="4">
+        <v>0.83200000000000007</v>
+      </c>
+      <c r="F624" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H624">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I624">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="625" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A625" s="1">
+        <v>4</v>
+      </c>
+      <c r="B625" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C625" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D625" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E625" s="4">
+        <v>0.78799999999999992</v>
+      </c>
+      <c r="F625" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H625">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I625">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="626" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A626" s="1">
+        <v>5</v>
+      </c>
+      <c r="B626" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C626" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D626" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E626" s="4">
+        <v>0.74400000000000011</v>
+      </c>
+      <c r="F626" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H626">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I626">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="627" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A627" s="1">
+        <v>6</v>
+      </c>
+      <c r="B627" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C627" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D627" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E627" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="F627" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H627">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I627">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="628" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A628" s="1">
+        <v>7</v>
+      </c>
+      <c r="B628" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C628" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D628" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E628" s="4">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="F628" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H628">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I628">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="629" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A629" s="1">
+        <v>8</v>
+      </c>
+      <c r="B629" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C629" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D629" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E629" s="4">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="F629" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G629" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H629">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>3</v>
+      </c>
+      <c r="I629">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="630" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A630" s="1">
+        <v>9</v>
+      </c>
+      <c r="B630" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C630" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D630" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E630" s="4">
+        <v>0.63</v>
+      </c>
+      <c r="F630" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H630">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I630">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="631" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A631" s="1">
+        <v>10</v>
+      </c>
+      <c r="B631" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C631" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D631" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E631" s="4">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="F631" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H631">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I631">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="632" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A632" s="1">
+        <v>11</v>
+      </c>
+      <c r="B632" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C632" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D632" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E632" s="4">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="F632" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H632">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I632">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="633" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A633" s="1">
+        <v>12</v>
+      </c>
+      <c r="B633" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C633" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D633" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E633" s="4">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="F633" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H633">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I633">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="634" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A634" s="1">
+        <v>13</v>
+      </c>
+      <c r="B634" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C634" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D634" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E634" s="4">
+        <v>0.58700000000000008</v>
+      </c>
+      <c r="F634" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H634">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I634">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="635" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A635" s="1">
+        <v>14</v>
+      </c>
+      <c r="B635" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C635" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D635" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E635" s="4">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="F635" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G635" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H635">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>4</v>
+      </c>
+      <c r="I635">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="636" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A636" s="1">
+        <v>15</v>
+      </c>
+      <c r="B636" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C636" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D636" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E636" s="4">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="F636" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H636">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I636">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="637" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A637" s="1">
+        <v>16</v>
+      </c>
+      <c r="B637" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C637" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D637" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E637" s="4">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="F637" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H637">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I637">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="638" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A638" s="1">
+        <v>17</v>
+      </c>
+      <c r="B638" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C638" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D638" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E638" s="4">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="F638" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H638">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I638">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="639" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A639" s="1">
+        <v>18</v>
+      </c>
+      <c r="B639" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C639" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D639" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E639" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F639" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H639">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I639">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="640" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A640" s="1">
+        <v>19</v>
+      </c>
+      <c r="B640" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C640" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D640" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E640" s="4">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="F640" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H640">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I640">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="641" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A641" s="1">
+        <v>20</v>
+      </c>
+      <c r="B641" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C641" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D641" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E641" s="4">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="F641" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H641">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I641">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="642" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A642" s="1">
+        <v>21</v>
+      </c>
+      <c r="B642" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C642" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D642" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E642" s="4">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="F642" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H642">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I642">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="643" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A643" s="1">
+        <v>22</v>
+      </c>
+      <c r="B643" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C643" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D643" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E643" s="4">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="F643" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H643">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I643">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="644" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A644" s="1">
+        <v>23</v>
+      </c>
+      <c r="B644" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C644" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D644" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E644" s="4">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="F644" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H644">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I644">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="645" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A645" s="1">
+        <v>24</v>
+      </c>
+      <c r="B645" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C645" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D645" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E645" s="4">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="F645" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H645">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I645">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="646" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A646" s="1">
+        <v>25</v>
+      </c>
+      <c r="B646" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C646" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D646" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E646" s="4">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="F646" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H646">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I646">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="647" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A647" s="1">
+        <v>26</v>
+      </c>
+      <c r="B647" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C647" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D647" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E647" s="4">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="F647" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H647">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I647">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="648" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A648" s="1">
+        <v>27</v>
+      </c>
+      <c r="B648" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C648" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D648" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E648" s="4">
+        <v>0.32</v>
+      </c>
+      <c r="F648" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H648">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I648">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="649" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A649" s="1">
+        <v>28</v>
+      </c>
+      <c r="B649" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C649" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D649" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E649" s="4">
+        <v>0.317</v>
+      </c>
+      <c r="F649" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H649">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I649">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="650" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A650" s="1">
+        <v>29</v>
+      </c>
+      <c r="B650" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C650" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D650" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E650" s="4">
+        <v>0.313</v>
+      </c>
+      <c r="F650" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H650">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I650">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="651" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A651" s="1">
+        <v>30</v>
+      </c>
+      <c r="B651" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C651" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D651" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E651" s="4">
+        <v>0.313</v>
+      </c>
+      <c r="F651" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H651">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I651">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="652" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A652" s="1">
+        <v>31</v>
+      </c>
+      <c r="B652" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C652" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D652" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E652" s="4">
+        <v>0.31</v>
+      </c>
+      <c r="F652" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H652">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I652">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="653" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A653" s="1">
+        <v>32</v>
+      </c>
+      <c r="B653" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C653" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D653" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E653" s="4">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="F653" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H653">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I653">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="654" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A654" s="1">
+        <v>33</v>
+      </c>
+      <c r="B654" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C654" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D654" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E654" s="4">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="F654" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H654">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I654">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="655" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A655" s="1">
+        <v>34</v>
+      </c>
+      <c r="B655" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C655" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D655" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E655" s="4">
+        <v>0.26</v>
+      </c>
+      <c r="F655" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H655">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I655">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="656" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A656" s="1">
+        <v>35</v>
+      </c>
+      <c r="B656" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C656" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D656" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E656" s="4">
+        <v>0.254</v>
+      </c>
+      <c r="F656" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G656" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H656">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>5</v>
+      </c>
+      <c r="I656">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="657" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A657" s="1">
+        <v>36</v>
+      </c>
+      <c r="B657" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C657" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D657" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E657" s="4">
+        <v>0.21</v>
+      </c>
+      <c r="F657" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H657">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I657">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="658" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A658" s="1">
+        <v>37</v>
+      </c>
+      <c r="B658" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C658" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D658" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E658" s="4">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="F658" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H658">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I658">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="659" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A659" s="1">
+        <v>38</v>
+      </c>
+      <c r="B659" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C659" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D659" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E659" s="4">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="F659" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H659">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I659">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="660" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A660" s="1">
+        <v>39</v>
+      </c>
+      <c r="B660" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C660" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D660" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E660" s="4">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="F660" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H660">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I660">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="661" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A661" s="1">
+        <v>40</v>
+      </c>
+      <c r="B661" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C661" t="s">
+        <v>510</v>
+      </c>
+      <c r="D661" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E661" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="F661" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H661">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I661">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="662" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A662" s="1">
+        <v>41</v>
+      </c>
+      <c r="B662" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C662" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D662" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E662" s="4">
+        <v>0.107</v>
+      </c>
+      <c r="F662" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H662">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I662">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="663" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A663" s="1">
+        <v>42</v>
+      </c>
+      <c r="B663" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C663" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D663" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E663" s="4">
+        <v>0.104</v>
+      </c>
+      <c r="F663" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H663">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I663">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="664" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A664" s="1">
+        <v>43</v>
+      </c>
+      <c r="B664" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C664" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D664" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E664" s="4">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="F664" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H664">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I664">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="665" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A665" s="1">
+        <v>44</v>
+      </c>
+      <c r="B665" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C665" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D665" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E665" s="4">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="F665" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H665">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I665">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="666" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A666" s="1">
+        <v>45</v>
+      </c>
+      <c r="B666" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C666" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D666" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E666" s="4">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="F666" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H666">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I666">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="667" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A667" s="1">
+        <v>46</v>
+      </c>
+      <c r="B667" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C667" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D667" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E667" s="4">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="F667" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H667">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I667">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="668" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A668" s="1">
+        <v>47</v>
+      </c>
+      <c r="B668" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C668" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D668" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E668" s="4">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="F668" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H668">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I668">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="669" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A669" s="1">
+        <v>48</v>
+      </c>
+      <c r="B669" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C669" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D669" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E669" s="4">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="F669" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H669">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I669">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="670" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A670" s="1">
+        <v>49</v>
+      </c>
+      <c r="B670" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C670" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D670" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E670" s="4">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="F670" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H670">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I670">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="671" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A671" s="1">
+        <v>50</v>
+      </c>
+      <c r="B671" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C671" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D671" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E671" s="4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F671" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H671">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I671">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="672" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A672" s="10">
+        <v>51</v>
+      </c>
+      <c r="B672" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C672" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D672" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E672" s="5">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F672" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H672">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I672">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="673" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A673" s="1">
+        <v>0</v>
+      </c>
+      <c r="B673" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C673" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D673" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E673" s="4">
+        <v>0.83400000000000007</v>
+      </c>
+      <c r="F673" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G673" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H673">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>1</v>
+      </c>
+      <c r="I673">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="674" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A674" s="1">
+        <v>1</v>
+      </c>
+      <c r="B674" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C674" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D674" t="s">
+        <v>1398</v>
+      </c>
+      <c r="E674" s="4">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="F674" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G674" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H674">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>2</v>
+      </c>
+      <c r="I674">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="675" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A675" s="1">
+        <v>2</v>
+      </c>
+      <c r="B675" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C675" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D675" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E675" s="4">
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="F675" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H675">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I675">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="676" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A676" s="1">
+        <v>3</v>
+      </c>
+      <c r="B676" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C676" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D676" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E676" s="4">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="F676" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G676" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H676">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>3</v>
+      </c>
+      <c r="I676">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="677" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A677" s="1">
+        <v>4</v>
+      </c>
+      <c r="B677" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C677" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D677" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E677" s="4">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="F677" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H677">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I677">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="678" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A678" s="1">
+        <v>5</v>
+      </c>
+      <c r="B678" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C678" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D678" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E678" s="4">
+        <v>0.373</v>
+      </c>
+      <c r="F678" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H678">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I678">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="679" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A679" s="1">
+        <v>6</v>
+      </c>
+      <c r="B679" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C679" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D679" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E679" s="4">
+        <v>0.35899999999999999</v>
+      </c>
+      <c r="F679" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G679" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H679">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>4</v>
+      </c>
+      <c r="I679">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="680" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A680" s="1">
+        <v>7</v>
+      </c>
+      <c r="B680" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C680" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D680" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E680" s="4">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="F680" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H680">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I680">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="681" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A681" s="1">
+        <v>8</v>
+      </c>
+      <c r="B681" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C681" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D681" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E681" s="4">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="F681" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H681">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I681">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="682" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A682" s="1">
+        <v>9</v>
+      </c>
+      <c r="B682" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C682" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D682" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E682" s="4">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="F682" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H682">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I682">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="683" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A683" s="1">
+        <v>10</v>
+      </c>
+      <c r="B683" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C683" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D683" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E683" s="4">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="F683" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H683">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I683">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="684" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A684" s="1">
+        <v>11</v>
+      </c>
+      <c r="B684" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C684" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D684" t="s">
+        <v>1419</v>
+      </c>
+      <c r="E684" s="4">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="F684" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H684">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I684">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="685" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A685" s="1">
+        <v>12</v>
+      </c>
+      <c r="B685" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C685" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D685" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E685" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="F685" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H685">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I685">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="686" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A686" s="1">
+        <v>13</v>
+      </c>
+      <c r="B686" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C686" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D686" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E686" s="4">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="F686" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H686">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I686">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="687" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A687" s="1">
+        <v>14</v>
+      </c>
+      <c r="B687" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C687" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D687" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E687" s="4">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="F687" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H687">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I687">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="688" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A688" s="1">
+        <v>15</v>
+      </c>
+      <c r="B688" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C688" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D688" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E688" s="4">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="F688" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H688">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I688">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="689" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A689" s="1">
+        <v>16</v>
+      </c>
+      <c r="B689" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C689" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D689" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E689" s="4">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="F689" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H689">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I689">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="690" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A690" s="1">
+        <v>17</v>
+      </c>
+      <c r="B690" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C690" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D690" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E690" s="4">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="F690" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H690">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I690">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="691" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A691" s="1">
+        <v>18</v>
+      </c>
+      <c r="B691" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C691" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D691" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E691" s="4">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="F691" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G691" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H691">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>5</v>
+      </c>
+      <c r="I691">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="692" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A692" s="1">
+        <v>19</v>
+      </c>
+      <c r="B692" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C692" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D692" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E692" s="4">
+        <v>0.252</v>
+      </c>
+      <c r="F692" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H692">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I692">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="693" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A693" s="1">
+        <v>20</v>
+      </c>
+      <c r="B693" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C693" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D693" t="s">
+        <v>1437</v>
+      </c>
+      <c r="E693" s="4">
+        <v>0.245</v>
+      </c>
+      <c r="F693" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H693">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I693">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="694" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A694" s="1">
+        <v>21</v>
+      </c>
+      <c r="B694" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C694" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D694" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E694" s="4">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="F694" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H694">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I694">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="695" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A695" s="1">
+        <v>22</v>
+      </c>
+      <c r="B695" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C695" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D695" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E695" s="4">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="F695" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H695">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I695">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="696" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A696" s="1">
+        <v>23</v>
+      </c>
+      <c r="B696" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C696" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D696" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E696" s="4">
+        <v>0.223</v>
+      </c>
+      <c r="F696" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H696">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I696">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="697" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A697" s="1">
+        <v>24</v>
+      </c>
+      <c r="B697" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C697" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D697" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E697" s="4">
+        <v>0.21</v>
+      </c>
+      <c r="F697" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H697">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I697">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="698" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A698" s="1">
+        <v>25</v>
+      </c>
+      <c r="B698" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C698" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D698" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E698" s="4">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="F698" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H698">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I698">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="699" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A699" s="1">
+        <v>26</v>
+      </c>
+      <c r="B699" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C699" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D699" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E699" s="4">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="F699" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H699">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I699">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="700" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A700" s="1">
+        <v>27</v>
+      </c>
+      <c r="B700" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C700" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D700" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E700" s="4">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="F700" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H700">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I700">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="701" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A701" s="1">
+        <v>28</v>
+      </c>
+      <c r="B701" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C701" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D701" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E701" s="4">
+        <v>0.192</v>
+      </c>
+      <c r="F701" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H701">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I701">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="702" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A702" s="1">
+        <v>29</v>
+      </c>
+      <c r="B702" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C702" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D702" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E702" s="4">
+        <v>0.187</v>
+      </c>
+      <c r="F702" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H702">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I702">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="703" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A703" s="1">
+        <v>30</v>
+      </c>
+      <c r="B703" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C703" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D703" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E703" s="4">
+        <v>0.187</v>
+      </c>
+      <c r="F703" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H703">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I703">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="704" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A704" s="1">
+        <v>31</v>
+      </c>
+      <c r="B704" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C704" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D704" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E704" s="4">
+        <v>0.184</v>
+      </c>
+      <c r="F704" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H704">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I704">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="705" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A705" s="1">
+        <v>32</v>
+      </c>
+      <c r="B705" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C705" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D705" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E705" s="4">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="F705" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H705">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I705">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="706" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A706" s="1">
+        <v>33</v>
+      </c>
+      <c r="B706" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C706" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D706" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E706" s="4">
+        <v>0.158</v>
+      </c>
+      <c r="F706" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H706">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I706">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="707" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A707" s="10">
+        <v>34</v>
+      </c>
+      <c r="B707" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C707" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D707" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E707" s="5">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="F707" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H707">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I707">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="708" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A708" s="1">
+        <v>0</v>
+      </c>
+      <c r="B708" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C708" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D708" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E708" s="4">
+        <v>0.93900000000000006</v>
+      </c>
+      <c r="F708" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G708" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H708" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>1</v>
+      </c>
+      <c r="I708" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="709" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A709" s="1">
+        <v>1</v>
+      </c>
+      <c r="B709" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C709" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D709" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E709" s="4">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="F709" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G709" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H709" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>2</v>
+      </c>
+      <c r="I709" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="710" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A710" s="1">
+        <v>2</v>
+      </c>
+      <c r="B710" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C710" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D710" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E710" s="4">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="F710" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H710" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I710" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="711" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A711" s="1">
+        <v>3</v>
+      </c>
+      <c r="B711" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C711" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D711" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E711" s="4">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="F711" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H711" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I711" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="712" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A712" s="1">
+        <v>4</v>
+      </c>
+      <c r="B712" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C712" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D712" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E712" s="4">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="F712" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H712" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I712" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="713" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A713" s="1">
+        <v>5</v>
+      </c>
+      <c r="B713" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C713" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D713" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E713" s="4">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="F713" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H713" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I713" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="714" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A714" s="1">
+        <v>6</v>
+      </c>
+      <c r="B714" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C714" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D714" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E714" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="F714" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H714" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I714" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="715" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A715" s="1">
+        <v>7</v>
+      </c>
+      <c r="B715" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C715" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D715" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E715" s="4">
+        <v>0.57600000000000007</v>
+      </c>
+      <c r="F715" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H715" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I715" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="716" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A716" s="1">
+        <v>8</v>
+      </c>
+      <c r="B716" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C716" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D716" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E716" s="4">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F716" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G716" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H716" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>3</v>
+      </c>
+      <c r="I716" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="717" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A717" s="1">
+        <v>9</v>
+      </c>
+      <c r="B717" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C717" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D717" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E717" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="F717" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H717" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I717" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="718" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A718" s="1">
+        <v>10</v>
+      </c>
+      <c r="B718" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C718" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D718" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E718" s="4">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="F718" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H718" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I718" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="719" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A719" s="1">
+        <v>11</v>
+      </c>
+      <c r="B719" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C719" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D719" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E719" s="4">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="F719" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H719" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I719" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="720" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A720" s="1">
+        <v>12</v>
+      </c>
+      <c r="B720" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C720" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D720" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E720" s="4">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="F720" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G720" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H720" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>4</v>
+      </c>
+      <c r="I720" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="721" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A721" s="1">
+        <v>13</v>
+      </c>
+      <c r="B721" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C721" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D721" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E721" s="4">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="F721" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H721" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I721" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="722" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A722" s="1">
+        <v>14</v>
+      </c>
+      <c r="B722" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C722" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D722" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E722" s="4">
+        <v>0.48099999999999998</v>
+      </c>
+      <c r="F722" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H722" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I722" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="723" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A723" s="1">
+        <v>15</v>
+      </c>
+      <c r="B723" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C723" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D723" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E723" s="4">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="F723" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H723" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I723" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="724" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A724" s="1">
+        <v>16</v>
+      </c>
+      <c r="B724" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C724" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D724" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E724" s="4">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="F724" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H724" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I724" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="725" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A725" s="1">
+        <v>17</v>
+      </c>
+      <c r="B725" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C725" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D725" t="s">
+        <v>1504</v>
+      </c>
+      <c r="E725" s="4">
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="F725" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H725" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I725" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="726" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A726" s="1">
+        <v>18</v>
+      </c>
+      <c r="B726" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C726" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D726" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E726" s="4">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="F726" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H726" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I726" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="727" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A727" s="1">
+        <v>19</v>
+      </c>
+      <c r="B727" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C727" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D727" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E727" s="4">
+        <v>0.441</v>
+      </c>
+      <c r="F727" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H727" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I727" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="728" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A728" s="1">
+        <v>20</v>
+      </c>
+      <c r="B728" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C728" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D728" t="s">
+        <v>1510</v>
+      </c>
+      <c r="E728" s="4">
+        <v>0.434</v>
+      </c>
+      <c r="F728" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H728" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I728" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="729" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A729" s="1">
+        <v>21</v>
+      </c>
+      <c r="B729" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C729" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D729" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E729" s="4">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="F729" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H729" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I729" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="730" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A730" s="1">
+        <v>22</v>
+      </c>
+      <c r="B730" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C730" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D730" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E730" s="4">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="F730" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G730" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H730" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>5</v>
+      </c>
+      <c r="I730" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+      <c r="J730" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="731" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A731" s="1">
+        <v>23</v>
+      </c>
+      <c r="B731" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C731" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D731" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E731" s="4">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="F731" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H731" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I731" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="732" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A732" s="1">
+        <v>24</v>
+      </c>
+      <c r="B732" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C732" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D732" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E732" s="4">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="F732" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H732" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I732" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="733" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A733" s="1">
+        <v>25</v>
+      </c>
+      <c r="B733" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C733" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D733" t="s">
+        <v>1520</v>
+      </c>
+      <c r="E733" s="4">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="F733" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H733" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I733" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="734" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A734" s="1">
+        <v>26</v>
+      </c>
+      <c r="B734" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C734" t="s">
+        <v>1521</v>
+      </c>
+      <c r="D734" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E734" s="4">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="F734" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H734" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I734" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="735" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A735" s="1">
+        <v>27</v>
+      </c>
+      <c r="B735" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C735" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D735" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E735" s="4">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="F735" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H735" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I735" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="736" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A736" s="1">
+        <v>28</v>
+      </c>
+      <c r="B736" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C736" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D736" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E736" s="4">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="F736" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H736" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I736" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="737" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A737" s="1">
+        <v>29</v>
+      </c>
+      <c r="B737" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C737" t="s">
+        <v>1527</v>
+      </c>
+      <c r="D737" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E737" s="4">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="F737" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H737" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I737" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="738" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A738" s="1">
+        <v>30</v>
+      </c>
+      <c r="B738" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C738" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D738" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E738" s="4">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="F738" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H738" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I738" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="739" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A739" s="1">
+        <v>31</v>
+      </c>
+      <c r="B739" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C739" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D739" t="s">
+        <v>1532</v>
+      </c>
+      <c r="E739" s="4">
+        <v>0.318</v>
+      </c>
+      <c r="F739" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H739" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I739" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="740" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A740" s="1">
+        <v>32</v>
+      </c>
+      <c r="B740" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C740" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D740" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E740" s="4">
+        <v>0.313</v>
+      </c>
+      <c r="F740" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H740" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I740" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="741" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A741" s="1">
+        <v>33</v>
+      </c>
+      <c r="B741" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C741" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D741" t="s">
+        <v>1536</v>
+      </c>
+      <c r="E741" s="4">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="F741" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H741" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I741" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="742" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A742" s="1">
+        <v>34</v>
+      </c>
+      <c r="B742" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C742" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D742" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E742" s="4">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="F742" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H742" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I742" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="743" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A743" s="1">
+        <v>35</v>
+      </c>
+      <c r="B743" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C743" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D743" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E743" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="F743" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H743" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I743" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="744" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A744" s="1">
+        <v>36</v>
+      </c>
+      <c r="B744" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C744" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D744" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E744" s="4">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="F744" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H744" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I744" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="745" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A745" s="1">
+        <v>37</v>
+      </c>
+      <c r="B745" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C745" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D745" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E745" s="4">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="F745" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H745" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I745" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="746" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A746" s="1">
+        <v>38</v>
+      </c>
+      <c r="B746" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C746" t="s">
+        <v>1545</v>
+      </c>
+      <c r="D746" t="s">
+        <v>1546</v>
+      </c>
+      <c r="E746" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F746" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H746" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I746" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="747" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A747" s="1">
+        <v>39</v>
+      </c>
+      <c r="B747" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C747" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D747" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E747" s="4">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="F747" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H747" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I747" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="748" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A748" s="1">
+        <v>40</v>
+      </c>
+      <c r="B748" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C748" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D748" t="s">
+        <v>643</v>
+      </c>
+      <c r="E748" s="4">
+        <v>6.2E-2</v>
+      </c>
+      <c r="F748" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H748" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I748" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="749" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A749" s="1">
+        <v>41</v>
+      </c>
+      <c r="B749" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C749" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D749" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E749" s="4">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="F749" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H749" s="11">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I749" s="11">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="750" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A750" s="10">
+        <v>42</v>
+      </c>
+      <c r="B750" s="12" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C750" s="12" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D750" s="12" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E750" s="5">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="F750" s="12" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G750" s="12"/>
+      <c r="H750" s="13">
+        <f>IFERROR(_xlfn.XLOOKUP(Table1[[#This Row],[Marker]],Table2[Marker],Table2[ID]),-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="I750" s="13">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Game]],Table14[Game],Table14[release_year])</f>
+        <v>2016</v>
+      </c>
+      <c r="J750" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -30322,10 +34836,16 @@
     <hyperlink ref="F84" r:id="rId21" xr:uid="{7955DA96-D951-4DB1-9C69-770A7A5846DF}"/>
     <hyperlink ref="F138" r:id="rId22" xr:uid="{378A9F0A-2FF4-418D-A30B-953488AD6AEF}"/>
     <hyperlink ref="F139" r:id="rId23" xr:uid="{AE361ED0-0A2F-4EEC-8839-F1B1DFA6E3C0}"/>
+    <hyperlink ref="F621" r:id="rId24" xr:uid="{A04F14F3-2768-4352-92F0-D47A9327082D}"/>
+    <hyperlink ref="F622" r:id="rId25" xr:uid="{A9863AB9-08F7-488B-94B8-2F1084A32C04}"/>
+    <hyperlink ref="F673" r:id="rId26" xr:uid="{5CFBB050-8F0B-4E57-B0C6-42A608B87C8C}"/>
+    <hyperlink ref="F674" r:id="rId27" xr:uid="{4FA67790-F0B8-41B7-9A17-61DBA070FDE4}"/>
+    <hyperlink ref="F708" r:id="rId28" xr:uid="{0C735E18-E3C6-408B-B8FC-858C1A0B8060}"/>
+    <hyperlink ref="F709" r:id="rId29" xr:uid="{BCFFEC87-1DEB-4999-9B76-4BA0AD67AFD6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId24"/>
+    <tablePart r:id="rId30"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -30334,7 +34854,7 @@
           <x14:formula1>
             <xm:f>Markers!$B$2:$B$8</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G620</xm:sqref>
+          <xm:sqref>G2:G750</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -30344,10 +34864,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36152F60-E18C-4F65-A7AA-DBBD526332AA}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="17.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1174</v>
       </c>
@@ -30363,8 +34886,11 @@
       <c r="E1" t="s">
         <v>1284</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <f t="shared" ref="A2:A12" si="0">ROW()-1</f>
         <v>1</v>
@@ -30382,8 +34908,11 @@
       <c r="E2">
         <v>2024</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -30401,8 +34930,11 @@
       <c r="E3">
         <v>2023</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -30420,8 +34952,11 @@
       <c r="E4">
         <v>2022</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -30439,8 +34974,11 @@
       <c r="E5">
         <v>2019</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -30458,8 +34996,11 @@
       <c r="E6">
         <v>2025</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -30477,8 +35018,11 @@
       <c r="E7">
         <v>2017</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -30496,8 +35040,11 @@
       <c r="E8">
         <v>2025</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -30515,8 +35062,11 @@
       <c r="E9">
         <v>2022</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -30534,8 +35084,11 @@
       <c r="E10">
         <v>2020</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -30553,8 +35106,11 @@
       <c r="E11">
         <v>2025</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -30572,8 +35128,11 @@
       <c r="E12">
         <v>2025</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>ROW()-1</f>
         <v>12</v>
@@ -30590,6 +35149,75 @@
       </c>
       <c r="E13">
         <v>2017</v>
+      </c>
+      <c r="F13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f>ROW()-1</f>
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C14">
+        <v>2638890</v>
+      </c>
+      <c r="D14" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table14[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/2638890/stats/</v>
+      </c>
+      <c r="E14">
+        <v>2026</v>
+      </c>
+      <c r="F14">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f>ROW()-1</f>
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C15">
+        <v>1809540</v>
+      </c>
+      <c r="D15" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table14[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/1809540/stats/</v>
+      </c>
+      <c r="E15">
+        <v>2024</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f>ROW()-1</f>
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C16">
+        <v>374320</v>
+      </c>
+      <c r="D16" s="11" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table14[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/374320/stats/</v>
+      </c>
+      <c r="E16">
+        <v>2016</v>
+      </c>
+      <c r="F16">
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
